--- a/光伏配储项目/电价数据/2026/盘龙站.xlsx
+++ b/光伏配储项目/电价数据/2026/盘龙站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.33631</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38457</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.90813</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.37681</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.40137</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.367</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.40133</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.34749</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.34644</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.34589</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.33028</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.33797</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.32888</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.33887</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.33641</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.32956</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.33203</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.32237</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.3332</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.33087</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.33174</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.33165</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.35093</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.33948</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.35263</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.3507</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.35656</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.35632</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.35563</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.3293</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.32265</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30823</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.30127</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.30686</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.30602</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.32175</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.31493</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.3091</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.26324</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.29153</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.26023</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.27586</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.26036</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.27367</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.32642</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.32635</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.33827</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.30894</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.07196</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.21197</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.16966</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.2625</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.25095</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.25559</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.24024</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.17794</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.30471</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.31503</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.28536</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.28423</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.29587</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.28462</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.30455</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.33166</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.34712</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.6508999999999999</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.63049</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.81775</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.39831</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.41538</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.46084</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.47202</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.72438</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>1.06853</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.5536599999999999</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.4491</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.49983</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.28731</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.44677</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.59918</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.75908</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.54537</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.83938</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.90928</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.40711</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>1.64324</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>1.01272</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.9286799999999999</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.8782300000000001</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.5769</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.5297799999999999</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.51187</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.4516</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.46355</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.74799</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.9529500000000001</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>1.00725</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.48801</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.5085500000000001</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.49735</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.49676</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.47754</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.39551</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.46035</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.3752200000000001</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.37258</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.33063</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33496</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.34488</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.32967</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.32991</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.32355</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.32823</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.32211</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.34111</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.3474</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.43776</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.37318</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.42498</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.40107</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.36202</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.37559</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34615</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.34054</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.36733</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.45992</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.34523</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.3452</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.35523</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.36405</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.31308</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.30473</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.29775</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.35143</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.42898</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.45047</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.6454800000000001</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.60725</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.76376</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.28928</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.31771</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.3221</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.29241</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.31133</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.23687</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.5767</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.48685</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.39856</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.36331</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.34332</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.34152</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.61983</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.37558</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.36985</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.87278</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.5949</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.738</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.77747</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.31713</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.31921</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.91811</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.44232</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.30617</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.50795</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.18277</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.29086</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.70884</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.12012</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.94713</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>1.1568</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>1.03076</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>1.2409</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.94845</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.44348</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.91072</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.9248200000000001</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.44325</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.42335</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.43788</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33234</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37327</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35307</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33422</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.49969</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.4804</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.4851</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.36802</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.43954</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.4095299999999999</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.36464</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.38642</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.37968</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36091</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.42262</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.43726</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33467</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.36766</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39178</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36412</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.36518</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35362</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.35885</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.34962</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.33947</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.34502</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.37375</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.389</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.46558</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.44049</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.43295</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34649</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39089</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35127</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36719</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34642</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.16033</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.20249</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.26931</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.34664</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.35139</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.11652</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.71238</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.60014</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.34794</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.5901799999999999</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.7617699999999999</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.76179</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.76032</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.77765</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.80664</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.8633999999999999</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.89303</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.9866</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.52163</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.54753</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.7645700000000001</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.7661399999999999</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.64725</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.65386</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.50512</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.6748099999999999</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.37209</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.37785</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.45808</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.51117</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.52022</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.58661</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.62838</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.60942</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.63735</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.16835</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.6030399999999999</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.70921</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.46423</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.51029</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.59761</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.70897</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.73364</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.82817</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.44881</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.62517</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.43788</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.51495</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.58172</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.73602</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.5569299999999999</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.8191499999999999</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.67495</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.5945</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.54332</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.69584</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.43461</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.45127</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.39438</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36193</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34773</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.3414700000000001</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.5485599999999999</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.52485</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.45881</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.39558</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.3946</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.3981</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.37197</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.36177</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.39785</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.39533</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.36552</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.4671</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.36007</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.34748</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.36396</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.36001</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.36164</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.33685</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.33456</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.33154</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.33323</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.33187</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.34966</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33775</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35287</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.39265</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.39765</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.3486</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.37993</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.34349</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.39119</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.42634</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.44868</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.3573</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.44667</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.34031</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.37764</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.34889</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.32849</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.47135</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.36069</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.35545</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.34738</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.5793400000000001</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.48459</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.46923</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.38002</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.23613</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.29828</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.8119299999999999</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.36827</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.34099</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.3249</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.39797</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.54044</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.34672</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.32021</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.31766</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.34532</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.47643</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.42093</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.38144</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.30633</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.38271</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.36047</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.44399</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.56362</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.3375</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.44464</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.45063</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.43344</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.39185</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.4453</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.52216</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.6115499999999999</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.46478</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.6733300000000001</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.5023299999999999</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.46926</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.50241</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.4415</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.4214</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.4020899999999999</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.39562</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.35692</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.37308</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.34461</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.34039</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32242</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.3127200000000001</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.3171</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.3164</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.30094</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.3701</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.37448</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.37407</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.3538</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.34015</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.32794</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.32763</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.3312</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32045</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31886</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31582</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31826</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.3187</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31513</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31679</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.31198</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.31336</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.31823</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.31579</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.30998</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31331</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31453</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.31938</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.31981</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.30823</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.3208</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.34436</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.30068</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.28649</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.31927</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.3141600000000001</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.3302</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.31883</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.30381</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.28977</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.28804</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.32062</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.3093</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.14358</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.31525</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.02809</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.30415</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.29821</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.29354</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.3192</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.32244</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.30312</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.40599</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.38857</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.2646</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.25792</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.23918</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.30484</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.26768</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.04531</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.26355</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.29737</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.29978</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.30086</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.30494</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33571</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33584</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.32694</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.33927</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.34924</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.34099</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.35111</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34845</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.35121</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.36419</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.3687</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.44074</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.35695</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.36878</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.36395</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.43924</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.34302</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35191</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34291</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.34975</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.31982</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.3548</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.3628</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.30798</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.25666</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.26076</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.23466</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.32026</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.29328</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.32973</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.20236</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.2665</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.1547</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.25699</v>
+      </c>
+      <c r="O122" t="n">
+        <v>-0.03256000000000001</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.31954</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.30657</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.30736</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.17436</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.25452</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.22415</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.20268</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.2581</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.18555</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.30766</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.25605</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.27669</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.32435</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.21209</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.27088</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10424</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04447</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04697999999999999</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04409</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04482999999999999</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.32348</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.01027</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.20669</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.04951</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.27613</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.1963</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.35528</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0456</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04369</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04335</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04549</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04339</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>0.01412</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.0453</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04538</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04358</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04422</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.06084000000000001</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.05905</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04985</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.0474</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04790999999999999</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19975</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14272</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28993</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30454</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29282</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29328</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29225</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29677</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30855</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.3453</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.3392</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.32665</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.34032</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.34333</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.31728</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.30426</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.28656</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31003</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.36219</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.32845</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.31939</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30704</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29442</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17236</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17092</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15943</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23612</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22651</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26883</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28566</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28083</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27069</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28091</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31625</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29728</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.40182</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.37712</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.42379</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.44897</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41843</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41527</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.37254</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40241</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29929</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15654</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29427</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31342</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31267</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34627</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30067</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33082</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38545</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6220399999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78461</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49797</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92039</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49456</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9142</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86287</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.2962</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35363</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.88749</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.6316000000000001</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18707</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.87046</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.66376</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33083</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.0329</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.53077</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.7909700000000001</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.57586</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.7729600000000001</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.7775299999999999</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8767699999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87386</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49314</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39866</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.39987</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44993</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20698</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87883</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55102</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62183</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53832</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49769</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45581</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42425</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43714</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.44846</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38817</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45268</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.4192</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.32992</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.39333</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.35429</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.37841</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.38958</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.40096</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.32531</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.37569</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.3294</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.32658</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.32118</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.32381</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.32179</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34744</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.44422</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.32284</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.36644</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.3277</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.46071</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.33041</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.5400900000000001</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.60885</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.86097</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.4377799999999999</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.2994</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.45059</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.35784</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.57467</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.36155</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.7888999999999999</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.87501</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.32931</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.32863</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.5187999999999999</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.29294</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.26857</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.40731</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.5313</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.39966</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31052</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.33063</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.31645</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32662</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.40648</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.32331</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.313</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.31954</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.32606</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.30731</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.34636</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.28742</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.32246</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.29406</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29591</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.2962</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.30587</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.18983</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.26607</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.26612</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.28031</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.26623</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.28438</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.32668</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.29556</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.31262</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.31051</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.3028</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.29719</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.29638</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.31063</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.31108</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.31277</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.31359</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.2967</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.32583</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32835</v>
+      </c>
+      <c r="C125" t="n">
+        <v>1.06972</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.31181</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.37857</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.33378</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.34157</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.34101</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.3175</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.32138</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.32126</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.31039</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.3149</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.29727</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.30279</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.3102200000000001</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.30426</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.29828</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.2967</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.32497</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.30767</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.30361</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.30078</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.30168</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.30167</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.30294</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.30339</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.30039</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.27032</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.29362</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.29885</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.29575</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.3079</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.31058</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.30435</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.30421</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.27405</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.3122</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.40695</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.31555</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.29757</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30418</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30136</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.38447</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.30603</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.46443</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.29488</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.27255</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.19053</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.29008</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.29888</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.30721</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.2682</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.29553</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.29593</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.29289</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.29246</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.25478</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.23657</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.23794</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.2558</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.16061</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.25122</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.17607</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.23406</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.23087</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.21836</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.23941</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.27939</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.29311</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.24211</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.28984</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.27447</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.29086</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.29165</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.26186</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.28186</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.28591</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.28488</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.26773</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.29004</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.29372</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.30554</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.30052</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.29726</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.30771</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.29762</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.40225</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.31101</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.38359</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.28269</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.32361</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.31424</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.29876</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.29325</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.3052</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.19284</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.7003200000000001</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.30481</v>
+      </c>
+      <c r="E126" t="n">
+        <v>0.92813</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.58036</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.68671</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.53883</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.21244</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.19836</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.37319</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.42081</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.38888</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.32747</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.34726</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.36251</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.33033</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.32357</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.36052</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.37444</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.29898</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.39218</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.35659</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.29463</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.29524</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.34523</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.38782</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.29823</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.36052</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.38566</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.29473</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.28516</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.34679</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.28899</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.43506</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.33543</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.15556</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.2336</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.23839</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.30888</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.28285</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.30431</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.28959</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.23732</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.27498</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.41533</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.3202</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.24027</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.28719</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.13806</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.2528</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>-0.04163</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.31403</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30073</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.24413</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.22302</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.29639</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.27469</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.23548</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.25233</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.27117</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.26373</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.29414</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.29537</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.25094</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.29073</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.26125</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.2818</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.32609</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.32219</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.31537</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.32093</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.30349</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.26787</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.3263</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.30406</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.27822</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.31394</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.32199</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.3101</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.43906</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.32187</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.57668</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.32146</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.31969</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.31608</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.36149</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.3094</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.31213</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.29286</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.26396</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.28942</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.24489</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.2706</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.25033</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.24454</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.16309</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.30713</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.18895</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.19801</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.18228</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.1951</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.15722</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.22773</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.24775</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.24554</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.27662</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.13098</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.13288</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.24553</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.25883</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.27224</v>
+      </c>
+      <c r="W127" t="n">
+        <v>-0.01896</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.15684</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.20299</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>-0.02023</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.18411</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.18069</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.18593</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.26181</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.28934</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.21536</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.26859</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.16315</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.28475</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.19996</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.27938</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.13544</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.18909</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.26891</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.25886</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.2978</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.33257</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.27822</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.2866</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.27763</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.26711</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.26217</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.26172</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.27366</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.28633</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.28497</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.26478</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.27192</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.29956</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.273</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.29794</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.27817</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.27902</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.29882</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.29125</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.28221</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.2876</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.28657</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.2881</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.30123</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31832</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.30636</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.28685</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.2906</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.3024</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.30911</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.30543</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.3131</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.29753</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.29824</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.3026</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.29905</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.30287</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.2988</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.304</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.31547</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.30144</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.30658</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.30989</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.45052</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.35878</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.34833</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.36203</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.35672</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.29002</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.29223</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.25671</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.28644</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.29323</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.33529</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.38109</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.3293</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.32287</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.31798</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.30417</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.30698</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.30761</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.3167</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.36904</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.35636</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.32047</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.31277</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.31868</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.31063</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.30426</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.30007</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.29954</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.30372</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.2991</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.29772</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.29949</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.29772</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.30421</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.3135</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.30139</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.30691</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.30461</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.3041</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.29473</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.3043</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.2972</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.30262</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.31105</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.33293</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.28343</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.2965</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31614</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.30394</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.28585</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.3165</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.28556</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.32358</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.3105</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.29232</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.30175</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.30206</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.28219</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30224</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.30457</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.32354</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31702</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.31821</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.3207</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.29552</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.31698</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.33543</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.29761</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.29222</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.3342</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.29596</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.29684</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.30928</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.34381</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.34574</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.32729</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.31313</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.35775</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.43633</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.36349</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.34538</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.32777</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.33277</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.40467</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.35548</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.41514</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.51936</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.36646</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.38837</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.35512</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.34251</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.32649</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.32492</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.40136</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.32935</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.32921</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.35398</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.33207</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.34333</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.29478</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.31985</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.32309</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.31126</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.31274</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.32102</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.31225</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.31312</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.35071</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.33337</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.3164</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.30755</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.29369</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.29776</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.29131</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.29578</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.29756</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.30099</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.30304</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.31896</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.29825</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.29888</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.29866</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.31518</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.31064</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.2966</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.31195</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.30747</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.29771</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.29943</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.29976</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.29594</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.3631</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.31438</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.31786</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.31088</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.29882</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.30793</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.35159</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.4508</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>1.45551</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.46784</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.82782</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.42957</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.5754</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.49713</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.41298</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.50732</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.59205</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.43098</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.49237</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.3994</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.6851499999999999</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.27932</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.35582</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.32258</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.46607</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.29579</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.38316</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.39905</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.86409</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.48543</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.40544</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.50968</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.47992</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.46526</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.67691</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.48844</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.48077</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.5333</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.44048</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.5234500000000001</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.38247</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.39687</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.36047</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.35177</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.42635</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.39827</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.36849</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.69857</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.52827</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.49192</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.5580499999999999</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.43336</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.7166399999999999</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.39157</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.31801</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.36406</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.3342</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.34668</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.48157</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.20972</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.33699</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.33989</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.29532</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.32133</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.30228</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.25738</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.28977</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>-0.0299</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.20057</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32003</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.31525</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.29437</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.38682</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.28836</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.28199</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.28473</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.28585</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.20931</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.20109</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.27852</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.28188</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.2784700000000001</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.27774</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.2777</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.27786</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.20301</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.29749</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.20029</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.16631</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.24144</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.29221</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.29539</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.26688</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.20003</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.20566</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.20932</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.21304</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.18014</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.17105</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.22001</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.2405</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.28915</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.32806</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.34831</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.34053</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.30385</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.35633</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.30067</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.31892</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32938</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.31965</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.29675</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.27355</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.29431</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.29308</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.28655</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.28999</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.25392</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.29054</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.29846</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.28344</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.29527</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.29685</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.30394</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.29351</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.2805299999999999</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.28219</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.26015</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.27316</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.27811</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.22366</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.29264</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.36555</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.33522</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.31743</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.31926</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.29332</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.30256</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.32776</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.3155</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.30466</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.30338</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.2820299999999999</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.29124</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.29552</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.31835</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.29262</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.33864</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.33055</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.28032</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.33174</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.2917</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.33322</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.2836</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.29618</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.34198</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.24538</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.32387</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.28515</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.3373</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.20455</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.16718</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.32207</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.24274</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.32167</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.2959</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.32262</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.32162</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.32264</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.32359</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.32306</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.32227</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.28571</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.32162</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.31847</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.01082</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.31926</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.29334</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.29011</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.27825</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.3118</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.31227</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.2895</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.28939</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.29661</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.28698</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.31182</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.28838</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.28902</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.27785</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.31727</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.2879</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.29405</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.29359</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.30855</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.28472</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.27803</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.2887</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.2963</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.27819</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.28841</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.27321</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.29389</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.30161</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.30842</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.31701</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.30232</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.31268</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.3067</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.3106</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.30797</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.30627</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32898</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.3179</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37007</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32535</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.31821</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.3096</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.36029</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.3217</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.32914</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.32259</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32394</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.31908</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.32123</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.32292</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.3058</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.32112</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.3229</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.32362</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.32711</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.32751</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.32553</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.33185</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.35066</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.32229</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.32393</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.33567</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.31854</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.33099</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.3459100000000001</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.32094</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.33195</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.32834</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.33031</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.32892</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.33994</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.43875</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.32662</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.34802</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.72013</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.71274</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.3655</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.21903</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.36536</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.33873</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.32259</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.35528</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.33143</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.31185</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.30017</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.38338</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.34852</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.32635</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.33428</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.33142</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.33109</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.33425</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.33034</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.31848</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.33121</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.32507</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.33222</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.31577</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.32835</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.32431</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.31477</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.33171</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.33204</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.31984</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.2903</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.33101</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.32874</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.3323</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.3323</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.31383</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.33811</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.35212</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.3288</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.32871</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.32342</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.3241</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.33015</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.3204</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.30951</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.41957</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.32004</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.32937</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.32178</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.33795</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.31984</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.32232</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.33677</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.34804</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.33389</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.31477</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.31878</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.33192</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.3352</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.33378</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.33174</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.3277</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.3211</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.32461</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.32118</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.3411</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.33939</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.32893</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.33159</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.33454</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.33048</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.3379</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.33182</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.34425</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.35604</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.45363</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.38667</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.34614</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33474</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.4193</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.36943</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.354</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.3237</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.3559</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.39968</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.54495</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.51012</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.77137</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.7176699999999999</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.78025</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.3503</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.94147</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.37632</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.5057900000000001</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.44802</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.5709299999999999</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.45453</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.52607</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.38267</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.34896</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.32524</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.32396</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.3244</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.34713</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.3203</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.31753</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.3457</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.34338</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.36697</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.34617</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.38574</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.32724</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.32598</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.32591</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.32291</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.32747</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.32635</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.32653</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.36695</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.34064</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.34196</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.33235</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.36028</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.31838</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.31512</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.31769</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.31527</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.29554</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.31042</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.31823</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.3025</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.29433</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.30819</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.31495</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.32304</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.32178</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.32394</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.32219</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.45366</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.44277</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.43139</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.50591</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.55386</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.6141599999999999</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.58456</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.40678</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.32042</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.32684</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.34737</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.33689</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.35828</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.40792</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.38745</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.36567</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.3243</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.35956</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.34736</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.44957</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.67565</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.4078</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.96594</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.39839</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.50351</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.35092</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.36742</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.35385</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.3395899999999999</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.3543</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.33786</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.33251</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.31475</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.2967</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.32732</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.31402</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.32197</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.35663</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.36661</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.30697</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.32506</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.3356</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.33032</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.33872</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.3203</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.33396</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.33143</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.33686</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.34624</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.35237</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.44725</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.33612</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.3919</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.38709</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.34995</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.39973</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.87507</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.68084</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.64471</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.36556</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.34492</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.33009</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.33405</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.3272</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.32914</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.34867</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.32911</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.32989</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.32832</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.40671</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.39664</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.32515</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.38837</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.31924</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.28002</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.29495</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.29933</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.31808</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.3137</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.31851</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.3097200000000001</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.33244</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.32924</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.33821</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.02499</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.2826</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.28935</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.3321</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.33821</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.2838</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.29072</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.35177</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.29687</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.33363</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.3274</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.35174</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.37479</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.33535</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.36254</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.37167</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.32775</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.35892</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35146</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.32815</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.32078</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.34057</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.34684</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.36401</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.40623</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.36539</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.34702</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.36511</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>0.6624</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.39356</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.38279</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.42657</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.39484</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.43635</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.43144</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.43195</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.36206</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.36118</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.34752</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.34568</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.34037</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.31714</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.3207</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.31624</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.29211</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.30374</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.3008</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.30748</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.32991</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.31961</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.38255</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.31876</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.21453</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.39152</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.38973</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.34377</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.38033</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.30827</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.21399</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.21097</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.23072</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.26742</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.24955</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.21826</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.34259</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.27463</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.33218</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.29498</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.334</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.28973</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.18338</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.29665</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.16218</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.1923</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.18395</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.20339</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.19138</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.29983</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.26796</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.23761</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.29821</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.22866</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.17976</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.02342</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.26601</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.01927</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.01949</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.17997</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.009089999999999999</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.21032</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.32368</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.17879</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.01778</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.16878</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.1736</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.20609</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.17108</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.17395</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.17682</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.01654</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.17969</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.01634</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>-0.00701</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.19121</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.19142</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.16083</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.28563</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>-0.01856</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.31973</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.24881</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.30006</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.26738</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.19918</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.28075</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.32424</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.23519</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.32772</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.31784</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.21373</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.29705</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.30626</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.10708</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.3012</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.00357</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.28415</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.29528</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.31325</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.34371</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.32907</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.31637</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.3068</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.33456</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.32113</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.2626</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.28519</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.29713</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.30488</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.25718</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.31227</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.28795</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.28419</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.29872</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.30299</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.32538</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.30959</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.30185</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.25913</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.26408</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.29741</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.30711</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.31019</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.28059</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.26354</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.28142</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.27494</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.26459</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.23028</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.22975</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.21309</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.25553</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.25711</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.29715</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.25885</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.25743</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.18148</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.18958</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.25908</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.16891</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.27748</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.16645</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.22731</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.23522</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.29382</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.28011</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.27992</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.28602</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.2776</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.06136999999999999</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.19415</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.19106</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.27027</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.00945</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.2098</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.22947</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.22155</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.05128</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>-0.00109</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.01169</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.01168</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.01141</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.20453</v>
+      </c>
+      <c r="X136" t="n">
+        <v>-0.00174</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.01106</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.18551</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>-0.00107</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>-0.00108</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.30672</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.01287</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.004200000000000001</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.2466</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.04463</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>-0.00542</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00042</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.00034</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04958</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.12992</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.02201</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03958</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.01754</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04297</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.04089</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04861</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04827</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02446</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02935</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.04409</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04941</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>-0.0039</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.2719</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04965</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04933</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.0401</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.03121</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04965</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.03715</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.19382</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.26108</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.28248</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.27486</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.27786</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.28735</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.01241</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.28461</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.2944</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.31392</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.30875</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.30252</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.28383</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.29675</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.31091</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.29583</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.29843</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.31867</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.31614</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.30564</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.29537</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.32021</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.32204</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.32196</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.31744</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.31591</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.31057</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.30785</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.29652</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.31569</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.30047</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.27513</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.37533</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.35357</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.30743</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.05087</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.28924</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.31429</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.29795</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.2866</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.18372</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.32015</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.17797</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.18249</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.17971</v>
+      </c>
+      <c r="P137" t="n">
+        <v>-0.00691</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.17562</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.16386</v>
+      </c>
+      <c r="S137" t="n">
+        <v>-0.0057</v>
+      </c>
+      <c r="T137" t="n">
+        <v>-0.03711</v>
+      </c>
+      <c r="U137" t="n">
+        <v>-0.0342</v>
+      </c>
+      <c r="V137" t="n">
+        <v>-0.008960000000000001</v>
+      </c>
+      <c r="W137" t="n">
+        <v>-0.00504</v>
+      </c>
+      <c r="X137" t="n">
+        <v>-0.04061</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.02112</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.02378</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.02852</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.41692</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.20864</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.2825</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.32628</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>-0.00882</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.24833</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>-0.01042</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.36456</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.8598</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.86146</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.32883</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.36192</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.09434999999999999</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.01117</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.25341</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.31389</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.3179</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.31897</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.27973</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.29602</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.29916</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.29232</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>0.42978</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.29626</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.29146</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.00215</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.29105</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.00149</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.31633</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.32056</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.31174</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.06856</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.30609</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.30243</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.3064</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.30786</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25453</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29189</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.47483</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.32033</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.31978</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.32793</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.33157</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.33624</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.31807</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.33275</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.3264</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.33786</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.93103</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.6395599999999999</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.43887</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.5057200000000001</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>1.05082</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>1.14704</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.45396</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.74095</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.52724</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.9725499999999999</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.97078</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.9765199999999999</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>1.10378</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.43974</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.52632</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.45365</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.34723</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.32346</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.35058</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.31307</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.31291</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.35148</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.37787</v>
+      </c>
+      <c r="E138" t="n">
+        <v>-0.03926</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.34518</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.5175700000000001</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.32105</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.30103</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.28181</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.35932</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.2744</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.20641</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.26589</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.26165</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.25461</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.22488</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.27783</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.21323</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.18098</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.20864</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.17514</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.17797</v>
+      </c>
+      <c r="X138" t="n">
+        <v>-0.0074</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.17516</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.19666</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.24441</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.32556</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.29907</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.25234</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.26234</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.29994</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.25908</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.28072</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.31622</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.35738</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.33888</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.33157</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.38382</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.31237</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.32924</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.33128</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.29958</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.31348</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.30758</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.31663</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.3191000000000001</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.30844</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.2584</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.31113</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.30229</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30203</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.32669</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.32031</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.31798</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.32161</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.3167</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.32649</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31413</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.31935</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.32114</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.32287</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32103</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.32111</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32035</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.3254</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.32028</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.31803</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.32342</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.31933</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.32965</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.34865</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.40938</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.37304</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.34903</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.34255</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.35177</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.32839</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.39938</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.33064</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.35473</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.3187</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.35891</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.35789</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.3169</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.33183</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.33002</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.3275</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.34696</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.31818</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.31313</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.30086</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.29655</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.29677</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.38209</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.3759</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.36752</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.33827</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.33874</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.33582</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.336</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.32695</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.32352</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.31755</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.31737</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.32851</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.31896</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.31813</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.32407</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.31752</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.30597</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.30566</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.29817</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.30174</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.30387</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.30394</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.31064</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.30565</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.31652</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.31141</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.31724</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.31641</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.32303</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.31614</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.32163</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.31753</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.36201</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.70247</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.34309</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.4849</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.384</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.33483</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.31299</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.32064</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.32642</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.33613</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.32649</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.33417</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.36511</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.33474</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.29689</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.33519</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.33068</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.33689</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.3347</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.33328</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.36898</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.3251</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.32262</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.32712</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.33117</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.32823</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.33269</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.32198</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.33005</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.33354</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.51613</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.45064</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.51344</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.30235</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.9710599999999999</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>1.041</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.45116</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.45177</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.6076699999999999</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.8824299999999999</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>1.02274</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.46771</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.7582000000000001</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.42213</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.36015</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.35413</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.43088</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.35907</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.35652</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.33026</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.35847</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.33509</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.34587</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.33468</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.33009</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.33775</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.33173</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.20475</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.32363</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.31183</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.32065</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.32049</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.43239</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.34885</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.33203</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.32719</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.32659</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.31941</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.31926</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.34797</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.32573</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.32425</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.31741</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.32164</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.32113</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.31819</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.31951</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.31911</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.30919</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.30334</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.30838</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.30364</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.3016</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.29781</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.32319</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.29862</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.30942</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.3152</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.30871</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.33904</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.31879</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.33359</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.33172</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.32204</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.36318</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.39099</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.34735</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.35367</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.43462</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.37967</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.34484</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.35705</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.33773</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.31048</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.3636</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.39292</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.35433</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.3737200000000001</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.34368</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29262</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.37158</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.35274</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.34357</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.34426</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31629</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.3367</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.34745</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32532</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33345</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.34154</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.33803</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.32483</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.34417</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.33915</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.34414</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.34669</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.36024</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.39241</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.36018</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.38536</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.36229</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.35791</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.42125</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.40351</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.64554</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.69689</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>1.7018</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>1.13207</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.74993</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>1.06483</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.5971599999999999</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.79604</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.68608</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.51242</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>1.0204</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.9162899999999999</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>1.58157</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>1.02083</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.87562</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.7278300000000001</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.36251</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.45631</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.35879</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.33415</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.33941</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.32339</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.32523</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.28582</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.33342</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.34592</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.31426</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.33261</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.32288</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.28885</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.30052</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.29422</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.30306</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.32603</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.29394</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.32589</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.31519</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.30563</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.30585</v>
+      </c>
+      <c r="S141" t="n">
+        <v>-0.00774</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.29239</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.29346</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.28857</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.32972</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.29677</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.28816</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.35842</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.35902</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.33672</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.30887</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.30717</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.31627</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.3143</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.32285</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.32588</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.3296</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.32762</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.33205</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.35218</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.36921</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.38632</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.32502</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.27683</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.43825</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.35243</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.58809</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.36954</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.35256</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.20148</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.38443</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.33143</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.30119</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.32761</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.43634</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.56263</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.35867</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.35399</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.32934</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.31657</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.33253</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.33673</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.32078</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.34701</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.34849</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.33017</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.33689</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.3470299999999999</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.34157</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.32851</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.39278</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.5325</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.34026</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.34746</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.35817</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.3683</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.44675</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.34049</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.3835</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.5051600000000001</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.40256</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.55338</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.4593</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.56202</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.75715</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.45076</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.5814400000000001</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.47223</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.50697</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.37953</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.37817</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.36951</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.34974</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.35021</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.33245</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.31296</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.32956</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34289</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.89742</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.44523</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.53011</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.48156</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.46788</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.34868</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.40001</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.36255</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.35383</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.35396</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.3551</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.36576</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.35793</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.35327</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.34362</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.35702</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.35679</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.35788</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.35294</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.34334</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.35062</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.35186</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.35292</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.3472</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.32871</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.34841</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.34107</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.36106</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.3503</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.33457</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.32776</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.33164</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.34113</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.34432</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.3407</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.33547</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.35951</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.36234</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.33988</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.36358</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.33475</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.34884</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.33381</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.33452</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.37321</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.31626</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.32318</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.3107</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.38765</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.32047</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.30664</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.2867</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.32569</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.44008</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.5290900000000001</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.30591</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.32411</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.32668</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.35109</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32329</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.354</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.35505</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.32313</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.34383</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.33887</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.33311</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.36628</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.37697</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.40947</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.39183</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.37466</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.34852</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.34586</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.36596</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.36261</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.35361</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.38566</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.37516</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.34356</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.36673</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.36349</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.36055</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.36406</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.51935</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.66165</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.49993</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.39436</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.48072</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.4837</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.42869</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.35111</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.33796</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.33926</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.34033</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.34008</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.34841</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.38165</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.36907</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.31297</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.37208</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.36016</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.35788</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.34441</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.34513</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.34141</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.34508</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.33803</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.34188</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.34868</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.32131</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.35684</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.34602</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.339</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.33075</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.33368</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.33148</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.33195</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.33753</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.33502</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.33727</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.32689</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.33153</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.3346</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.33219</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.33103</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.30607</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.3185</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.30994</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.17607</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.30465</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.29567</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.31168</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.14573</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.19861</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.14597</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.28763</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04751</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.12154</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.33317</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.22593</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.26026</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.1441</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.14522</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.28372</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.18834</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.30362</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.2268</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.26579</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.15513</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.36134</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.30873</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.16197</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.29972</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.31066</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.19897</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.18545</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.28887</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.28726</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.32545</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.32385</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.32045</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.30998</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.33981</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.34646</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.34874</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.35847</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.35952</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.36061</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.38209</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.43496</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.4030899999999999</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.34463</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.43583</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.32195</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.34879</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.05902</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.37697</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.37228</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.37166</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.36592</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.37701</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.38146</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.43326</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.39176</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.38706</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.36992</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.37742</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.38729</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.36428</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.36546</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.36996</v>
       </c>
     </row>
   </sheetData>
